--- a/python-net/_sample_files/developer-guide/advanced-usage/working-with-tables/extract-tables-from-document/data.xlsx
+++ b/python-net/_sample_files/developer-guide/advanced-usage/working-with-tables/extract-tables-from-document/data.xlsx
@@ -1,73 +1,601 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="16729"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alber\Sources\GroupDocs\GroupDocs.Text.Net\testdata\unit\xlsx\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18225" windowHeight="8160" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Inventory" sheetId="1" r:id="rId3"/>
+    <sheet name="Suppliers" sheetId="2" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="171027"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Jonas Weber</author>
+  </authors>
+  <commentList>
+    <comment ref="G2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Reorder placed with Northwind on 29 December.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Autumn Harvest roast: hold 60 bags for the January promotion.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>john</t>
-  </si>
-  <si>
-    <t>smith</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>first</t>
-  </si>
-  <si>
-    <t>second</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>d</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="174">
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Unit cost</t>
+  </si>
+  <si>
+    <t>On hand</t>
+  </si>
+  <si>
+    <t>Reorder level</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>HLP-CF-101</t>
+  </si>
+  <si>
+    <t>Harbor Blend whole bean coffee</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Northwind Coffee Roasters</t>
+  </si>
+  <si>
+    <t>1 kg bag</t>
+  </si>
+  <si>
+    <t>A-01</t>
+  </si>
+  <si>
+    <t>HLP-CF-102</t>
+  </si>
+  <si>
+    <t>Dockside Decaf whole bean coffee</t>
+  </si>
+  <si>
+    <t>HLP-CF-103</t>
+  </si>
+  <si>
+    <t>Lighthouse Espresso beans</t>
+  </si>
+  <si>
+    <t>A-02</t>
+  </si>
+  <si>
+    <t>HLP-CF-104</t>
+  </si>
+  <si>
+    <t>Cold brew concentrate</t>
+  </si>
+  <si>
+    <t>1 L bottle</t>
+  </si>
+  <si>
+    <t>HLP-CF-105</t>
+  </si>
+  <si>
+    <t>Autumn Harvest spiced roast</t>
+  </si>
+  <si>
+    <t>500 g bag</t>
+  </si>
+  <si>
+    <t>A-03</t>
+  </si>
+  <si>
+    <t>HLP-OL-201</t>
+  </si>
+  <si>
+    <t>Cold-pressed olive oil</t>
+  </si>
+  <si>
+    <t>Oils &amp; Vinegars</t>
+  </si>
+  <si>
+    <t>Grove &amp; Press</t>
+  </si>
+  <si>
+    <t>750 ml tin</t>
+  </si>
+  <si>
+    <t>B-04</t>
+  </si>
+  <si>
+    <t>HLP-OL-202</t>
+  </si>
+  <si>
+    <t>Pumpkin seed oil</t>
+  </si>
+  <si>
+    <t>250 ml bottle</t>
+  </si>
+  <si>
+    <t>HLP-OL-203</t>
+  </si>
+  <si>
+    <t>Apple cider vinegar</t>
+  </si>
+  <si>
+    <t>Orchard Row</t>
+  </si>
+  <si>
+    <t>500 ml bottle</t>
+  </si>
+  <si>
+    <t>B-05</t>
+  </si>
+  <si>
+    <t>HLP-OL-204</t>
+  </si>
+  <si>
+    <t>Aged balsamic vinegar</t>
+  </si>
+  <si>
+    <t>HLP-HN-301</t>
+  </si>
+  <si>
+    <t>Chestnut honey</t>
+  </si>
+  <si>
+    <t>Honey &amp; Preserves</t>
+  </si>
+  <si>
+    <t>Hillside Apiaries</t>
+  </si>
+  <si>
+    <t>350 g jar</t>
+  </si>
+  <si>
+    <t>C-02</t>
+  </si>
+  <si>
+    <t>HLP-HN-302</t>
+  </si>
+  <si>
+    <t>Wildflower honey</t>
+  </si>
+  <si>
+    <t>500 g jar</t>
+  </si>
+  <si>
+    <t>HLP-HN-303</t>
+  </si>
+  <si>
+    <t>Cranberry relish</t>
+  </si>
+  <si>
+    <t>300 g jar</t>
+  </si>
+  <si>
+    <t>C-03</t>
+  </si>
+  <si>
+    <t>HLP-HN-304</t>
+  </si>
+  <si>
+    <t>Fig and walnut preserve</t>
+  </si>
+  <si>
+    <t>HLP-HN-305</t>
+  </si>
+  <si>
+    <t>Autumn Harvest apple butter</t>
+  </si>
+  <si>
+    <t>HLP-GR-401</t>
+  </si>
+  <si>
+    <t>Maple pecan granola</t>
+  </si>
+  <si>
+    <t>Grains &amp; Cereals</t>
+  </si>
+  <si>
+    <t>Mill Creek Farms</t>
+  </si>
+  <si>
+    <t>750 g bag</t>
+  </si>
+  <si>
+    <t>D-01</t>
+  </si>
+  <si>
+    <t>HLP-GR-402</t>
+  </si>
+  <si>
+    <t>Stone-ground oats</t>
+  </si>
+  <si>
+    <t>HLP-GR-403</t>
+  </si>
+  <si>
+    <t>Heritage spelt flour</t>
+  </si>
+  <si>
+    <t>D-02</t>
+  </si>
+  <si>
+    <t>HLP-GR-404</t>
+  </si>
+  <si>
+    <t>Wild rice blend</t>
+  </si>
+  <si>
+    <t>HLP-GR-405</t>
+  </si>
+  <si>
+    <t>Autumn Harvest muesli</t>
+  </si>
+  <si>
+    <t>D-03</t>
+  </si>
+  <si>
+    <t>HLP-SP-501</t>
+  </si>
+  <si>
+    <t>Smoked sea salt</t>
+  </si>
+  <si>
+    <t>Spices &amp; Salts</t>
+  </si>
+  <si>
+    <t>Saltmarsh Co.</t>
+  </si>
+  <si>
+    <t>250 g jar</t>
+  </si>
+  <si>
+    <t>E-01</t>
+  </si>
+  <si>
+    <t>HLP-SP-502</t>
+  </si>
+  <si>
+    <t>Pink peppercorns</t>
+  </si>
+  <si>
+    <t>Spice Quay</t>
+  </si>
+  <si>
+    <t>100 g jar</t>
+  </si>
+  <si>
+    <t>HLP-SP-503</t>
+  </si>
+  <si>
+    <t>Mulling spice blend</t>
+  </si>
+  <si>
+    <t>80 g tin</t>
+  </si>
+  <si>
+    <t>E-02</t>
+  </si>
+  <si>
+    <t>HLP-SP-504</t>
+  </si>
+  <si>
+    <t>Smoked paprika</t>
+  </si>
+  <si>
+    <t>100 g tin</t>
+  </si>
+  <si>
+    <t>HLP-SP-505</t>
+  </si>
+  <si>
+    <t>Saffron threads</t>
+  </si>
+  <si>
+    <t>1 g vial</t>
+  </si>
+  <si>
+    <t>E-03</t>
+  </si>
+  <si>
+    <t>HLP-CH-601</t>
+  </si>
+  <si>
+    <t>Aged harbour cheddar</t>
+  </si>
+  <si>
+    <t>Cheese &amp; Dairy</t>
+  </si>
+  <si>
+    <t>Coastline Creamery</t>
+  </si>
+  <si>
+    <t>1 kg wheel</t>
+  </si>
+  <si>
+    <t>F-01</t>
+  </si>
+  <si>
+    <t>HLP-CH-602</t>
+  </si>
+  <si>
+    <t>Smoked gouda</t>
+  </si>
+  <si>
+    <t>HLP-CH-603</t>
+  </si>
+  <si>
+    <t>Goat cheese log</t>
+  </si>
+  <si>
+    <t>200 g log</t>
+  </si>
+  <si>
+    <t>F-02</t>
+  </si>
+  <si>
+    <t>HLP-CH-604</t>
+  </si>
+  <si>
+    <t>Cultured butter</t>
+  </si>
+  <si>
+    <t>250 g block</t>
+  </si>
+  <si>
+    <t>HLP-BK-701</t>
+  </si>
+  <si>
+    <t>Sea salt crackers</t>
+  </si>
+  <si>
+    <t>Bakery</t>
+  </si>
+  <si>
+    <t>Quayside Bakehouse</t>
+  </si>
+  <si>
+    <t>200 g box</t>
+  </si>
+  <si>
+    <t>G-01</t>
+  </si>
+  <si>
+    <t>HLP-BK-702</t>
+  </si>
+  <si>
+    <t>Rosemary flatbread</t>
+  </si>
+  <si>
+    <t>150 g box</t>
+  </si>
+  <si>
+    <t>HLP-BK-703</t>
+  </si>
+  <si>
+    <t>Oat and honey biscuits</t>
+  </si>
+  <si>
+    <t>250 g box</t>
+  </si>
+  <si>
+    <t>G-02</t>
+  </si>
+  <si>
+    <t>HLP-BK-704</t>
+  </si>
+  <si>
+    <t>Autumn Harvest fruit loaf</t>
+  </si>
+  <si>
+    <t>500 g loaf</t>
+  </si>
+  <si>
+    <t>HLP-TE-801</t>
+  </si>
+  <si>
+    <t>Harbor breakfast tea</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>Leaf &amp; Kettle</t>
+  </si>
+  <si>
+    <t>100 bags</t>
+  </si>
+  <si>
+    <t>H-01</t>
+  </si>
+  <si>
+    <t>HLP-TE-802</t>
+  </si>
+  <si>
+    <t>Chamomile and apple tea</t>
+  </si>
+  <si>
+    <t>50 bags</t>
+  </si>
+  <si>
+    <t>HLP-TE-803</t>
+  </si>
+  <si>
+    <t>Smoked lapsang tea</t>
+  </si>
+  <si>
+    <t>H-02</t>
+  </si>
+  <si>
+    <t>HLP-CN-901</t>
+  </si>
+  <si>
+    <t>Tomato passata</t>
+  </si>
+  <si>
+    <t>Pantry</t>
+  </si>
+  <si>
+    <t>Sunfield Kitchens</t>
+  </si>
+  <si>
+    <t>700 g jar</t>
+  </si>
+  <si>
+    <t>J-01</t>
+  </si>
+  <si>
+    <t>HLP-CN-902</t>
+  </si>
+  <si>
+    <t>Roasted red peppers</t>
+  </si>
+  <si>
+    <t>290 g jar</t>
+  </si>
+  <si>
+    <t>HLP-CN-903</t>
+  </si>
+  <si>
+    <t>Butter beans</t>
+  </si>
+  <si>
+    <t>400 g tin</t>
+  </si>
+  <si>
+    <t>J-02</t>
+  </si>
+  <si>
+    <t>HLP-CN-904</t>
+  </si>
+  <si>
+    <t>Chickpeas</t>
+  </si>
+  <si>
+    <t>HLP-CN-905</t>
+  </si>
+  <si>
+    <t>Autumn Harvest squash soup</t>
+  </si>
+  <si>
+    <t>600 ml jar</t>
+  </si>
+  <si>
+    <t>J-03</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Lines</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>orders@coastlinecreamery.example</t>
+  </si>
+  <si>
+    <t>orders@grovepress.example</t>
+  </si>
+  <si>
+    <t>orders@hillsideapiaries.example</t>
+  </si>
+  <si>
+    <t>orders@leafkettle.example</t>
+  </si>
+  <si>
+    <t>orders@millcreekfarms.example</t>
+  </si>
+  <si>
+    <t>alex.chen@northwindroasters.example</t>
+  </si>
+  <si>
+    <t>Oils &amp; Vinegars, Honey &amp; Preserves</t>
+  </si>
+  <si>
+    <t>orders@orchardrow.example</t>
+  </si>
+  <si>
+    <t>orders@quaysidebakehouse.example</t>
+  </si>
+  <si>
+    <t>orders@saltmarshco.example</t>
+  </si>
+  <si>
+    <t>orders@spicequay.example</t>
+  </si>
+  <si>
+    <t>orders@sunfieldkitchens.example</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,7 +606,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,40 +614,99 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -129,6 +716,37 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Inventory" displayName="Inventory" ref="A1:I41" totalsRowShown="0">
+  <autoFilter ref="A1:I41"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="SKU"/>
+    <tableColumn id="2" name="Product"/>
+    <tableColumn id="3" name="Category"/>
+    <tableColumn id="4" name="Supplier"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="Unit cost"/>
+    <tableColumn id="7" name="On hand"/>
+    <tableColumn id="8" name="Reorder level"/>
+    <tableColumn id="9" name="Location"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Suppliers" displayName="Suppliers" ref="A1:D12" totalsRowShown="0">
+  <autoFilter ref="A1:D12"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Supplier"/>
+    <tableColumn id="2" name="Categories"/>
+    <tableColumn id="3" name="Lines"/>
+    <tableColumn id="4" name="Contact"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -148,7 +766,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -160,7 +778,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -427,70 +1045,1401 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C4C0D4-6BE8-4F38-9FD0-ACEAD439BAA8}">
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="11.7142857142857" customWidth="1"/>
+    <col min="2" max="2" width="29.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="17.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="23.1428571428571" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="11.5714285714286" customWidth="1"/>
+    <col min="8" max="8" width="16.1428571428571" customWidth="1"/>
+    <col min="9" max="9" width="11.7142857142857" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="12.75">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="12.75">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="G2">
+        <v>240</v>
+      </c>
+      <c r="H2">
+        <v>80</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="12.75">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="G3">
+        <v>96</v>
+      </c>
+      <c r="H3">
+        <v>40</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="12.75">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1">
+        <v>21.75</v>
+      </c>
+      <c r="G4">
+        <v>180</v>
+      </c>
+      <c r="H4">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="12.75">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1">
+        <v>9.5999999999999996</v>
+      </c>
+      <c r="G5">
+        <v>150</v>
+      </c>
+      <c r="H5">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="12.75">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1">
+        <v>11.199999999999999</v>
+      </c>
+      <c r="G6">
+        <v>210</v>
+      </c>
+      <c r="H6">
+        <v>70</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="12.75">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="G7">
+        <v>320</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7" t="s">
         <v>32</v>
       </c>
     </row>
+    <row r="8" spans="1:9" ht="12.75">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1">
+        <v>8.75</v>
+      </c>
+      <c r="G8">
+        <v>140</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="12.75">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4.2999999999999998</v>
+      </c>
+      <c r="G9">
+        <v>260</v>
+      </c>
+      <c r="H9">
+        <v>80</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="12.75">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="1">
+        <v>14.6</v>
+      </c>
+      <c r="G10">
+        <v>85</v>
+      </c>
+      <c r="H10">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="12.75">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1">
+        <v>7.7999999999999998</v>
+      </c>
+      <c r="G11">
+        <v>190</v>
+      </c>
+      <c r="H11">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="12.75">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="1">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G12">
+        <v>230</v>
+      </c>
+      <c r="H12">
+        <v>80</v>
+      </c>
+      <c r="I12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="12.75">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4.9500000000000002</v>
+      </c>
+      <c r="G13">
+        <v>175</v>
+      </c>
+      <c r="H13">
+        <v>60</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="12.75">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="1">
+        <v>5.4000000000000004</v>
+      </c>
+      <c r="G14">
+        <v>120</v>
+      </c>
+      <c r="H14">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="12.75">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G15">
+        <v>205</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
+      <c r="I15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="12.75">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="1">
+        <v>6.2999999999999998</v>
+      </c>
+      <c r="G16">
+        <v>160</v>
+      </c>
+      <c r="H16">
+        <v>50</v>
+      </c>
+      <c r="I16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="12.75">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="1">
+        <v>3.1000000000000001</v>
+      </c>
+      <c r="G17">
+        <v>300</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="12.75">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3.8500000000000001</v>
+      </c>
+      <c r="G18">
+        <v>210</v>
+      </c>
+      <c r="H18">
+        <v>80</v>
+      </c>
+      <c r="I18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="12.75">
+      <c r="A19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G19">
+        <v>130</v>
+      </c>
+      <c r="H19">
+        <v>40</v>
+      </c>
+      <c r="I19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="12.75">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5.9000000000000004</v>
+      </c>
+      <c r="G20">
+        <v>180</v>
+      </c>
+      <c r="H20">
+        <v>60</v>
+      </c>
+      <c r="I20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="12.75">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3.9500000000000002</v>
+      </c>
+      <c r="G21">
+        <v>260</v>
+      </c>
+      <c r="H21">
+        <v>80</v>
+      </c>
+      <c r="I21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="12.75">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5.25</v>
+      </c>
+      <c r="G22">
+        <v>110</v>
+      </c>
+      <c r="H22">
+        <v>40</v>
+      </c>
+      <c r="I22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="12.75">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G23">
+        <v>145</v>
+      </c>
+      <c r="H23">
+        <v>50</v>
+      </c>
+      <c r="I23" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="12.75">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3.6000000000000001</v>
+      </c>
+      <c r="G24">
+        <v>190</v>
+      </c>
+      <c r="H24">
+        <v>60</v>
+      </c>
+      <c r="I24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="12.75">
+      <c r="A25" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="1">
+        <v>6.7999999999999998</v>
+      </c>
+      <c r="G25">
+        <v>70</v>
+      </c>
+      <c r="H25">
+        <v>25</v>
+      </c>
+      <c r="I25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="12.75">
+      <c r="A26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="G26">
+        <v>90</v>
+      </c>
+      <c r="H26">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="12.75">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27" s="1">
+        <v>15.199999999999999</v>
+      </c>
+      <c r="G27">
+        <v>75</v>
+      </c>
+      <c r="H27">
+        <v>25</v>
+      </c>
+      <c r="I27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="12.75">
+      <c r="A28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="1">
+        <v>4.7000000000000002</v>
+      </c>
+      <c r="G28">
+        <v>140</v>
+      </c>
+      <c r="H28">
+        <v>50</v>
+      </c>
+      <c r="I28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="12.75">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="1">
+        <v>3.8999999999999999</v>
+      </c>
+      <c r="G29">
+        <v>220</v>
+      </c>
+      <c r="H29">
+        <v>80</v>
+      </c>
+      <c r="I29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="12.75">
+      <c r="A30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2.8500000000000001</v>
+      </c>
+      <c r="G30">
+        <v>280</v>
+      </c>
+      <c r="H30">
+        <v>90</v>
+      </c>
+      <c r="I30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="12.75">
+      <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>114</v>
+      </c>
+      <c r="D31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" t="s">
+        <v>120</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2.9500000000000002</v>
+      </c>
+      <c r="G31">
+        <v>160</v>
+      </c>
+      <c r="H31">
+        <v>60</v>
+      </c>
+      <c r="I31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="12.75">
+      <c r="A32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" t="s">
+        <v>114</v>
+      </c>
+      <c r="D32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F32" s="1">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="G32">
+        <v>195</v>
+      </c>
+      <c r="H32">
+        <v>70</v>
+      </c>
+      <c r="I32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="12.75">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" t="s">
+        <v>127</v>
+      </c>
+      <c r="F33" s="1">
+        <v>4.75</v>
+      </c>
+      <c r="G33">
+        <v>85</v>
+      </c>
+      <c r="H33">
+        <v>30</v>
+      </c>
+      <c r="I33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="12.75">
+      <c r="A34" t="s">
+        <v>128</v>
+      </c>
+      <c r="B34" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="1">
+        <v>6.4000000000000004</v>
+      </c>
+      <c r="G34">
+        <v>170</v>
+      </c>
+      <c r="H34">
+        <v>60</v>
+      </c>
+      <c r="I34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="12.75">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F35" s="1">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="G35">
+        <v>120</v>
+      </c>
+      <c r="H35">
+        <v>40</v>
+      </c>
+      <c r="I35" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="12.75">
+      <c r="A36" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" t="s">
+        <v>130</v>
+      </c>
+      <c r="D36" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="1">
+        <v>7.0999999999999996</v>
+      </c>
+      <c r="G36">
+        <v>60</v>
+      </c>
+      <c r="H36">
+        <v>20</v>
+      </c>
+      <c r="I36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="12.75">
+      <c r="A37" t="s">
+        <v>140</v>
+      </c>
+      <c r="B37" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2.3999999999999999</v>
+      </c>
+      <c r="G37">
+        <v>340</v>
+      </c>
+      <c r="H37">
+        <v>120</v>
+      </c>
+      <c r="I37" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="12.75">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" t="s">
+        <v>142</v>
+      </c>
+      <c r="D38" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" t="s">
+        <v>148</v>
+      </c>
+      <c r="F38" s="1">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="G38">
+        <v>150</v>
+      </c>
+      <c r="H38">
+        <v>50</v>
+      </c>
+      <c r="I38" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="12.75">
+      <c r="A39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1.6000000000000001</v>
+      </c>
+      <c r="G39">
+        <v>410</v>
+      </c>
+      <c r="H39">
+        <v>150</v>
+      </c>
+      <c r="I39" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="12.75">
+      <c r="A40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" t="s">
+        <v>143</v>
+      </c>
+      <c r="E40" t="s">
+        <v>151</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="G40">
+        <v>390</v>
+      </c>
+      <c r="H40">
+        <v>150</v>
+      </c>
+      <c r="I40" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="12.75">
+      <c r="A41" t="s">
+        <v>155</v>
+      </c>
+      <c r="B41" t="s">
+        <v>156</v>
+      </c>
+      <c r="C41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" t="s">
+        <v>157</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3.7000000000000002</v>
+      </c>
+      <c r="G41">
+        <v>135</v>
+      </c>
+      <c r="H41">
+        <v>50</v>
+      </c>
+      <c r="I41" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:C2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId3"/>
+  <tableParts>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06F9039C-0D7F-410C-824F-82D25581BAA8}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="23.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="31.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="8.71428571428571" customWidth="1"/>
+    <col min="4" max="4" width="33.2857142857143" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>9</v>
+    <row r="1" spans="1:4" ht="12.75">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="12.75">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12.75">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.75">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="12.75">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="12.75">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="12.75">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="12.75">
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="12.75">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="12.75">
+      <c r="A10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="12.75">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="12.75">
+      <c r="A12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>